--- a/boltz_experiment_master.xlsx
+++ b/boltz_experiment_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39b8f5b1ceed89e2/Desktop/MSc_research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F261FCD-4EC3-4698-B7D0-2C9BD20FB552}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{826EA522-058E-47BE-B737-557D54C2899B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B693CC76-476B-46BE-908F-567C50EF84D4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
   <si>
     <t>Experiment ID</t>
   </si>
@@ -61,9 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CIF Result</t>
-  </si>
-  <si>
     <t>Outcome Summary</t>
   </si>
   <si>
@@ -189,10 +186,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>added two ligands</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Two ligands were successfully added, but their spatial arrangement is incorrect.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -294,10 +287,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>added eight ligands</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>008_fgfr2_ligand_x7_model.cif</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -307,6 +296,40 @@
   </si>
   <si>
     <t>The maximum number of ligands we can include without a Google Colab Pro subscription is seven.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009_fgfr2_pipeline</t>
+  </si>
+  <si>
+    <t>added 8 ligands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>added 2 ligands</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CIF/PDB Final Result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009_4_fgfr2_minimized.pdb</t>
+  </si>
+  <si>
+    <t>Google Colab: Boltz2; HPC: OpenMM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Develop a pipeline (Boltz2(add 7 ligands) → ChimeraX → OpenMM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>After energy minimisation, the overall protein conformation remained similar to the original structure, but the ligand was lost during the process.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -737,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155A3948-C683-4751-821F-C1EF1E91D33B}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -762,10 +785,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -780,320 +803,358 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
       <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" t="s">
         <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" t="s">
         <v>37</v>
-      </c>
-      <c r="I3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" t="s">
         <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" t="s">
         <v>52</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" t="s">
         <v>53</v>
-      </c>
-      <c r="I6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" t="s">
         <v>57</v>
-      </c>
-      <c r="I7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
         <v>62</v>
       </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" t="s">
         <v>64</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" t="s">
         <v>67</v>
       </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" t="s">
-        <v>72</v>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1121,42 +1182,42 @@
   <sheetData>
     <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>821</v>
       </c>
       <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1179,21 +1240,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="C1" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/boltz_experiment_master.xlsx
+++ b/boltz_experiment_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39b8f5b1ceed89e2/Desktop/MSc_research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{826EA522-058E-47BE-B737-557D54C2899B}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFDC983C-4944-495A-A4CD-9F1A5D9D7D54}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B693CC76-476B-46BE-908F-567C50EF84D4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="84">
   <si>
     <t>Experiment ID</t>
   </si>
@@ -303,9 +303,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>009_fgfr2_pipeline</t>
-  </si>
-  <si>
     <t>added 8 ligands</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -330,6 +327,30 @@
   </si>
   <si>
     <t>After energy minimisation, the overall protein conformation remained similar to the original structure, but the ligand was lost during the process.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>009_fgfr2_pipeline.yaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fgfr2_20lipids.yaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add 20 lipids around the protein using the HPC system.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HPC: Boltz2/OpenMM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Twenty lipids were successfully added to the protein, which means we can proceed with running the full pipeline on the HPC system.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -760,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155A3948-C683-4751-821F-C1EF1E91D33B}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -803,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>38</v>
@@ -914,7 +935,7 @@
         <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
         <v>45</v>
@@ -952,7 +973,7 @@
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
         <v>46</v>
@@ -1124,7 +1145,7 @@
         <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -1142,19 +1163,54 @@
         <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J10" t="s">
         <v>23</v>
       </c>
       <c r="K10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
         <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" t="s">
+        <v>82</v>
+      </c>
+      <c r="L11" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/boltz_experiment_master.xlsx
+++ b/boltz_experiment_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39b8f5b1ceed89e2/Desktop/MSc_research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFDC983C-4944-495A-A4CD-9F1A5D9D7D54}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61052453-9BF3-4352-BA6B-7CE583620FEB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B693CC76-476B-46BE-908F-567C50EF84D4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="95">
   <si>
     <t>Experiment ID</t>
   </si>
@@ -352,13 +352,74 @@
   <si>
     <t>Twenty lipids were successfully added to the protein, which means we can proceed with running the full pipeline on the HPC system.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HPC: Boltz2/Biopython/OpenMM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010_3_fgfr2_minimized.pdb</t>
+  </si>
+  <si>
+    <t>straighten the linker between the TM and ICD/ECD regions using Biopython</t>
+  </si>
+  <si>
+    <t>011_3_fgfr2_clean_minimized.pdb</t>
+  </si>
+  <si>
+    <t>OpenMM successfully minimized the energy after straightening the linker, but the linker between the TM and ICD does not appear reasonable based on UniProt information.</t>
+  </si>
+  <si>
+    <t>012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>use the Boltz2 prediction model generated in the test10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tune the linker between the TM and ICD and separate it from the ICD domain</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>012_3_fgfr2_clean_minimized.pdb</t>
+  </si>
+  <si>
+    <t>The conformation appears physically reasonable at this stage.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -391,6 +452,13 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -781,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155A3948-C683-4751-821F-C1EF1E91D33B}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -792,7 +860,7 @@
     <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.36328125" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.6328125" customWidth="1"/>
     <col min="10" max="10" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.08984375" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
@@ -1203,6 +1271,9 @@
       <c r="H11" t="s">
         <v>81</v>
       </c>
+      <c r="I11" t="s">
+        <v>86</v>
+      </c>
       <c r="J11" t="s">
         <v>23</v>
       </c>
@@ -1211,6 +1282,82 @@
       </c>
       <c r="L11" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/boltz_experiment_master.xlsx
+++ b/boltz_experiment_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/39b8f5b1ceed89e2/Desktop/MSc_research/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61052453-9BF3-4352-BA6B-7CE583620FEB}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{5F9DF5E2-6C68-4678-AFC6-E59FBBEA935A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C18D347-04D4-492C-9B72-EB6A182CC82C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B693CC76-476B-46BE-908F-567C50EF84D4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="100">
   <si>
     <t>Experiment ID</t>
   </si>
@@ -413,6 +413,49 @@
   </si>
   <si>
     <t>The conformation appears physically reasonable at this stage.</t>
+  </si>
+  <si>
+    <t>013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compiling all pipeline steps in Nextflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>013_3_fgfr2_clean_minimized.pdb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HPC: NextFlow (Boltz2/ChimeraX/Biopython/OpenMM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Overall, although the conformation in Test 13 is not as well</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>‑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>refined as that in Test 12, it remains acceptable for downstream analysis and is sufficient for executing the entire pipeline through a single Nextflow script.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -849,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{155A3948-C683-4751-821F-C1EF1E91D33B}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -1358,6 +1401,44 @@
       </c>
       <c r="L13" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
